--- a/Result/checksun_type/橡膠製品.xlsx
+++ b/Result/checksun_type/橡膠製品.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>32.45</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>32.52</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>32.18</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>32.18</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>632841.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>935929.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>935929.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2409414.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7448178.62</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7448178.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-924297.7577862795</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>632841</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>632841.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>32.27</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>32.55</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>32.14</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>32.14</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>617759.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1339194.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1339194</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>2624071.2</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7623153.62</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7623153.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-939129.5841430698</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>617759</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>617759.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>32.37</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>32.61</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>32.13</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>32.61</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>32.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>1051826.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1934963.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1934963.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>2669931.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7648029.54</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7648029.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-925161.6366476603</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>1051826</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1051826.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>32.77</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>32.67</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>32.13</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>32.13</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1516187.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2486774.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>2486774.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2653543.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7689107.16</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7689107.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-918673.1174882306</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1516187</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1516187.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>33.19</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>32.79</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>32.14</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>32.14</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>861035.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>3238258.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>3238258</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>2590767.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7722506.64</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>7722506.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-926347.0144930365</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>861035</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>861035.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>33.46</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>32.14</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>32.14</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>2649163.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>3882899.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>3882899.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>2652271.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>7742742.64</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>7742742.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-834031.0454108655</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>2649163</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2649163.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>33.49</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.07</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>32.15</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>3596605.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>3908948.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>3908948.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>2628346.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>7740611.7</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>7740611.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-863949.4093859475</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>3596605</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>3596605.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>33.17999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.16</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>32.14</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.16</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>32.14</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>3810884.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>3404899.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>3404899.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>2613777.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>7693111.92</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>7693111.92</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-977346.2361579947</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>3810884</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>3810884.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>32.66</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>33.24</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>32.11</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>32.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>5273603.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>2820312.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>2820312.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>3230075.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>7651550.02</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>7651550.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-1127394.944540991</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>5273603</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>5273603.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>32.2</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>33.27</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>32.09</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>33.27</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>32.09</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>4084242.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1943276.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1943276.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>3215441.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>7595786.58</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>7595786.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-1458206.02992595</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>4084242</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>4084242.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>31.93</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>33.46</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>32.08</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>32.08</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>2779408.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1421644.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1421644.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>3057314.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>7547083.92</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>7547083.92</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-1751282.97226425</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>2779408</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2779408.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>25.17</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>25.81</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>26.21</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>26.21</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2640500.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1250615.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1250615.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1106199.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>782665.72</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>782665.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>145958.8603834747</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2640500</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2640500.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>25.11</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>26.23</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>26.23</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>294019.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1104517.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1104517</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>887752.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>781130.98</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>781130.98</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>11002.73077159072</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>294019</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>294019.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>25.24</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>25.92</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>26.27</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>26.27</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>207586.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1192859.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1192859.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>928084.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>782391.16</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>782391.16</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>69223.98379848537</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>207586</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>207586.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>25.4</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>26.3</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>26.3</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1392190.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1262601.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1262601</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1000934.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>785880.42</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>785880.42</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>159185.5958441033</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1392190</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1392190.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>25.61</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>26.03</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>26.34</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>26.34</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1718782.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1182405.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1182405.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>932700.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>780344.38</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>780344.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>155095.1274862681</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1718782</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1718782.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>25.78</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>26.09</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>26.37</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>26.37</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>1910008.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>961784.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>961784</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>800813.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>781447.4</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>781447.4</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>108720.4895648509</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>1910008</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1910008.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>25.99</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>26.42</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>26.42</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>735733.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>670987.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>670987</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>667216.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>827462.7</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>827462.7</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>18099.63219265325</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>735733</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>735733.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>26.05</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>26.19</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>26.44</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>26.44</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>556292.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>663308.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>663308.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>643303.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>844020.8</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>844020.8</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>13810.02765406191</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>556292</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>556292.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>26.06</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>26.2</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>26.47</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>26.47</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>991212.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>739267.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>739267.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>598147.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>892876.2</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>892876.2</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>26414.62732557207</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>991212</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>991212.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>26.06</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>26.22</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>26.48</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>26.48</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>615675.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>682995.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>682995.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>512125.9</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>875433.98</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>875433.98</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-3120.752691041096</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>615675</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>615675.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>26.09</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>26.24</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>26.5</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>456023.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>639843.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>639843.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>521840.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>869848.4</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>869848.4</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-4966.590118665481</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>456023</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>456023.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>89.94</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>90.1</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>90.25</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>90.25</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>968537.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1825351.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1825351.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>1656564.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>2365506.24</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>2365506.24</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-188306.1429182813</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>968537</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>968537.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>89.88</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>90.12</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>90.28</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>90.12</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>90.28</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>195548.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1905143.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1905143.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>1671640.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2391849.02</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>2391849.02</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-152309.9573425211</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>195548</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>195548.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>89.92</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>90.15</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>90.32</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>90.31999999999999</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1140258.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>2416365.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>2416365.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>1822473.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>2415761.16</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>2415761.16</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-12626.94375777338</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1140258</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1140258.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>90.02000000000001</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>90.37</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>90.37</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>3365423.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>2473502.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>2473502.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>2161242.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>2425064.2</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>2425064.2</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>86152.2522117868</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>3365423</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>3365423.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>90.22</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>90.22</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>90.44</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>90.44</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>3456993.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1995642.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1995642</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1871315.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>2368198.92</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>2368198.92</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-14222.01255354774</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>3456993</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>3456993.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>90.35999999999999</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>90.26</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>90.5</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>90.26000000000001</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>90.5</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1367496.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1487778.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1487778</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1611835.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>2351178.14</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>2351178.14</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-166916.9617699708</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1367496</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1367496.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>90.5</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>90.28</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>90.55</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>90.55</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>2751658.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>1438138.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>1438138.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1577522.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>2365300.4</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>2365300.4</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-155216.6048730761</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>2751658</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>2751658.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>90.58</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>90.34</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>90.6</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>90.59999999999999</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>1425943.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1228582.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1228582</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1424130.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2331056.34</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2331056.34</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-281261.4305606168</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>1425943</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>1425943.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>90.56</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>90.32</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>90.64</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>90.64</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>976120.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1848982.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1848982.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1493719.9</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2341901.82</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2341901.82</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-309239.5233085097</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>976120</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>976120.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>90.46000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>90.28</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>90.71</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>90.70999999999999</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>917673.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1746988.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1746988.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1543528.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2357075.28</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2357075.28</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-289968.63711591</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>917673</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>917673.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>90.24000000000001</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>90.22</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>90.76</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>90.76000000000001</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>1119297.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1735893.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1735893</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1716171.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>2417664.08</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2417664.08</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-245820.5983723421</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>1119297</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>1119297.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>15.22</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>15.47</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>15.47</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>2045503.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>2018138.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>2018138</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>2236149.0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2554018.7</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2554018.7</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-86757.37066765525</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>2045503</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>2045503.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>15.23</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>15.49</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>452345.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>2048684.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>2048684.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>2187558.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2562490.98</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2562490.98</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-100644.552788794</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>452345</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>452345.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>15.24</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>15.52</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>3829227.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>2176127.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>2176127.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>2369743.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2582790.44</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2582790.44</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>53806.56392346416</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>3829227</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>3829227.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>15.23</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>15.55</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>15.55</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>2597401.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1874699.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1874699.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>2149755.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2546991.32</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2546991.32</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-89279.4323420052</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>2597401</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>2597401.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>15.32</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>15.58</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>15.58</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1166214.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1804780.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1804780.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>2013647.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>2543580.86</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>2543580.86</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-158518.0901376032</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1166214</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1166214.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>15.36</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>15.6</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>2198237.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>2454160.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>2454160</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>2037003.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>2588416.96</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>2588416.96</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-98427.63376925793</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>2198237</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>2198237.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>15.34</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>15.63</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>15.63</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>1089559.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>2326431.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>2326431.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>2041099.4</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>2566931.16</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>2566931.16</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-119642.7448941479</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>1089559</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>1089559.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>15.35</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>15.65</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>15.65</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>2322087.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>2563359.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>2563359</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>2075491.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>2563266.64</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2563266.64</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-26890.16275491426</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>2322087</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>2322087.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>15.32</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>15.67</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>2247805.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>2424812.2</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>2424812.2</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>2187003.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2542720.7</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2542720.7</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-25482.68245761935</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>2247805</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>2247805.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>15.18</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>15.14</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>15.68</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>15.68</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>4413112.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>2222514.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>2222514.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>2053449.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2514244.94</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2514244.94</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-14603.11480228323</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>4413112</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>4413112.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>15.08</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>15.7</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>15.7</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>1559595.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1619847.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1619847.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>1868397.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>2448102.82</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>2448102.82</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-230536.5140517214</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>1559595</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>1559595.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>22.45</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>22.27</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>22.96</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>22.96</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>7709077.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>6902362.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>6902362.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>10536459.4</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>18372156.56</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>18372156.56</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-1728046.904041458</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>7709077</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>7709077.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>22.27</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>22.27</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>22.98</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>8094728.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>6801509.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>6801509.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>13106952.6</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>18482859.8</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>18482859.8</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-1802758.697127396</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>8094728</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>8094728.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>22.16</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>22.27</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>23.02</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>5184610.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>7442964.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>7442964.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>13839888.8</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>18524829.46</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>18524829.46</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-1886425.340924187</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>5184610</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>5184610.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>22.23</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>23.08</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>23.08</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>8055991.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>8664583.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>8664583.800000001</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>13984362.3</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>18603102.24</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>18603102.24</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-1626778.427029451</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>8055991</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>8055991.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>22.44</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>22.36</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>23.13</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>23.13</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>5467406.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>10005910.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>10005910.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>14539208.8</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>18591061.06</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>18591061.06</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-1505402.999071633</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>5467406</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>5467406.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>22.67</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>22.42</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>23.19</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>7204814.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>14170556.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>14170556.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>14722882.3</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>18674616.78</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>18674616.78</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-1000896.744879337</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>7204814</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>7204814.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>22.86</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>22.48</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>23.25</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>11302002.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>19412395.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>19412395.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>15201942.7</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>18798632.24</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>18798632.24</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-430578.0694303662</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>11302002</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>11302002.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>22.82</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>22.54</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>23.31</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>23.31</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>11292706.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>20236813.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>20236813</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>14996972.1</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>18829844.06</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>18829844.06</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-39443.74488075078</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>11292706</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>11292706.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>22.59</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>22.58</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>23.36</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>14762623.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>19304140.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>19304140.8</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>15824223.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>18880145.34</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>18880145.34</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>521724.2810787261</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>14762623</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>14762623.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>22.22</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>22.59</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>23.4</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>23.4</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>26290637.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>19072507.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>19072507.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>15269800.2</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>18905583.06</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>18905583.06</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>932983.0581251681</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>26290637</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>26290637.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>21.94</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>22.58</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>23.43</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>23.43</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>33414009.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>15275208.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>15275208.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>14443763.6</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>18619973.2</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>18619973.2</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>252030.4161156155</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>33414009</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>33414009.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>23.73</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>23.83</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>23.83</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>3841626.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>2331040.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>2331040</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>2969556.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>3510707.8</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>3510707.8</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-130158.8157780841</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>3841626</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>3841626.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>23.65</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>23.67</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>23.83</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>23.83</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>1149930.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1995333.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1995333.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>2840568.8</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>3584204.64</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>3584204.64</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-260528.8972514691</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>1149930</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>1149930.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>23.62</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>23.68</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>23.83</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>23.83</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>3065205.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>3101267.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>3101267.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>2938534.5</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>3629368.38</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>3629368.38</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-149071.2673116084</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>3065205</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>3065205.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>23.65</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>23.69</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>23.84</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>23.84</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>2110183.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>3075754.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>3075754.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>2736390.1</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>3695306.06</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>3695306.06</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-189730.1435649646</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>2110183</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>2110183.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>23.69</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>23.84</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>23.84</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>1488256.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>3138189.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>3138189.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>2779340.2</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>3842793.44</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>3842793.44</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-138714.3902281537</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>1488256</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1488256.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>23.73</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>23.72</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>23.85</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>2163094.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>3608072.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>3608072.6</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>2841731.6</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>3951765.26</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>3951765.26</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>5754.378475439269</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>2163094</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>2163094.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>23.81</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>23.87</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>23.87</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>6679599.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>3685804.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>3685804</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>3447732.7</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>3952286.78</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>3952286.78</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>139628.7488207347</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>6679599</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>6679599.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>23.79</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>23.76</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>23.88</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>23.88</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>2937640.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>2775801.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>2775801.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>3116663.4</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>3890931.94</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>3890931.94</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-158020.1417152975</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>2937640</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>2937640.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>23.69</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>23.76</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>23.88</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>23.88</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>2422358.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>2397025.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>2397025.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>3305995.2</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>3888752.8</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>3888752.8</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-176665.0874197977</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>2422358</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>2422358.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>23.6</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>23.76</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>23.89</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>3837672.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>2420491.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>2420491</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>3668528.7</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>3913912.06</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>3913912.06</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-141782.4710183768</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>3837672</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>3837672.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>23.54</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>23.89</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>2551751.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>2075390.6</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>2075390.6</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>3503860.0</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>3883864.64</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>3883864.64</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-238527.2879085471</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>2551751</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>2551751.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>20.39</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>3111603.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>7746104.8</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>7746104.8</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>9050560.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>10123667.06</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>10123667.06</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-771459.655962158</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>3111603</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>3111603.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>20.32</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>20.32</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>7571166.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>8563180.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>8563180.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>11611277.8</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>10267424.2</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>10267424.2</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-297801.5701538436</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>7571166</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>7571166.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>20.32</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>20.41</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>16673233.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>8717070.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>8717070.199999999</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>11266208.8</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>10273960.5</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>10273960.5</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-88321.71292218566</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>16673233</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>16673233.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>20.28</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>20.41</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>7787838.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>7789054.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>7789054.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>10120826.8</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>10049815.34</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>10049815.34</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-761131.8914154526</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>7787838</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>7787838.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>20.47</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>3586684.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>8268244.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>8268244</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>10538446.3</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>10010900.14</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>10010900.14</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-743099.4002838545</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>3586684</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>3586684.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>20.66</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>20.34</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>20.34</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>7196981.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>10355016.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>10355016.4</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>11515321.2</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>10079136.34</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>10079136.34</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-240675.7915142905</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>7196981</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>7196981.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>20.85</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>20.39</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>20.35</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>8340615.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>14659375.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>14659375.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>11858116.5</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>10161117.42</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>10161117.42</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>98850.2492820248</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>8340615</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>8340615.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>20.89</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>20.38</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>20.35</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>12033153.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>13815347.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>13815347.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>12611250.0</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>10116463.34</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>10116463.34</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>457824.8700881209</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>12033153</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>12033153.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>20.88</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>20.38</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>20.35</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>10183787.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>12452599.4</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>12452599.4</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>12062049.2</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>10008415.46</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>10008415.46</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>558665.79730797</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>10183787</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>10183787.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>20.73</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>14020546.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>12808648.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>12808648.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>11848845.6</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>10016520.52</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>10016520.52</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>880918.2720038947</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>14020546</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>14020546.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>20.59</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>20.26</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>20.32</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>28718775.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>12675626.0</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>12675626</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>10947329.1</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>10085969.44</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>10085969.44</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>898736.261855077</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>28718775</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>28718775.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>32.27</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>32.02</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>34.46</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>34.46</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>404617627.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>334984338.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>334984338.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>343453991.7</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>254135261.9</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>254135261.9</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>13802493.4675678</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>404617627</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>404617627.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>32.29</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>32.02</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>34.56</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>34.56</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>224175271.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>326509219.2</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>326509219.2</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>348728858.4</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>249628764.78</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>249628764.78</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>8626825.81695652</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>224175271</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>224175271.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>32.23999999999999</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>32.03</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>34.68</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>34.68</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>477833499.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>337645841.4</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>337645841.4</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>352786261.8</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>248133853.62</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>248133853.62</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>20258023.5369063</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>477833499</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>477833499.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>32.21</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>32.05</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>34.8</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>330887312.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>296215602.8</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>296215602.8</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>336042950.1</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>240751409.92</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>240751409.92</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>8972852.153373599</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>330887312</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>330887312.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>32.26000000000001</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>32.09</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>34.93</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>34.93</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>237407983.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>304622507.4</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>304622507.4</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>327040481.7</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>236492706.78</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>236492706.78</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>8274954.064277887</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>237407983</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>237407983.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>32.26000000000001</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>32.14</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>35.04</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>35.04</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>362242031.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>351923645.0</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>351923645</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>323818175.6</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>233773096.16</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>233773096.16</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>16998065.11327398</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>362242031</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>362242031.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>32.16</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>32.18</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>35.16</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>35.16</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>279858382.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>370948497.6</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>370948497.6</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>311320263.8</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>229411904.14</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>229411904.14</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>15477502.00065148</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>279858382</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>279858382.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>32.12</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>32.26</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>35.28</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>270682306.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>367926682.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>367926682.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>310986590.8</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>226284722.84</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>226284722.84</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>21579320.58973897</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>270682306</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>270682306.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>31.96</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>32.34</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>35.39</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>32.34</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>35.39</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>372921835.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>375870297.4</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>375870297.4</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>306368218.7</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>223057972.7</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>223057972.7</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>30508665.26737326</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>372921835</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>372921835.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>31.73</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>32.42</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>35.49</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>35.49</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>473913671.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>349458456.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>349458456</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>294231970.2</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>218344839.58</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>218344839.58</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>31221041.51158744</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>473913671</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>473913671.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>31.7</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>32.55</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>35.6</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>457366294.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>295712706.2</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>295712706.2</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>267001738.8</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>211452866.52</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>211452866.52</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>20303130.80647963</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>457366294</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>457366294.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>14.15</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>14.55</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>15.33</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>15.33</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>68688077.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>101804803.0</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>101804803</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>74935011.2</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>30339431.62</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>30339431.62</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>15671107.87946576</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>68688077</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>68688077.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>13.95</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>14.58</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>15.37</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>15.37</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>92481687.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>99443449.0</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>99443449</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>70967530.1</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>29325671.72</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>29325671.72</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>19494028.09976791</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>92481687</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>92481687.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>13.86</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>14.61</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>15.41</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>15.41</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>269831215.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>92656108.4</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>92656108.40000001</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>63887757.6</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>27873508.06</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>27873508.06</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>21709812.05377927</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>269831215</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>269831215.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>14.05</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>15.48</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>15.48</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>33459639.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>49431112.0</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>49431112</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>38611636.3</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>22602446.32</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>22602446.32</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>5098132.129017681</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>33459639</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>33459639.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>14.25</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>14.78</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>15.54</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>15.54</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>44563397.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>51359969.2</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>51359969.2</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>37456953.6</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>22051610.12</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>22051610.12</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>6510610.660464764</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>44563397</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>44563397.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>14.41</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>15.6</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>56881307.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>48065219.4</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>48065219.4</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>34702680.9</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>21287472.88</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>21287472.88</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>7106226.967515431</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>56881307</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>56881307.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>14.59</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>15.67</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>58544984.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>42491611.2</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>42491611.2</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>30005442.9</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>20283236.36</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>20283236.36</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>6383537.514462251</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>58544984</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>58544984.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>14.68</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>14.98</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>15.72</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>15.72</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>53706233.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>35119406.8</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>35119406.8</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>25205107.9</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>19316153.86</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>19316153.86</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>4944889.420298357</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>53706233</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>53706233.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>14.68</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>15.77</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>15.77</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>43103925.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>27792160.6</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>27792160.6</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>21351073.8</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>18438625.82</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>18438625.82</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>3231512.270767849</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>43103925</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>43103925.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>14.65</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>15.81</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>15.81</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>28089648.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>23553938.0</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>23553938</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>18509204.1</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>17925870.48</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>17925870.48</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>1804381.047482558</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>28089648</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>28089648.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>14.69</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>15.86</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>15.86</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>29013266.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>21340142.4</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>21340142.4</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>16852186.3</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>17558334.48</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>17558334.48</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>1309852.512522049</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>29013266</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>29013266.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>19.83</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>19.56</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>4772715.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>8568182.0</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>8568182</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>12540322.7</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>9716875.84</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>9716875.84</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-514431.7435085755</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>4772715</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>4772715.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>19.68</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>19.56</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>6270038.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>10013239.4</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>10013239.4</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>12492670.5</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>9767333.66</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>9767333.66</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-98755.1101299338</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>6270038</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>6270038.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>19.64</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>19.57</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>19.57</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>9560056.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>11858500.4</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>11858500.4</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>12158130.3</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>9884923.4</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>9884923.4</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>338168.155772768</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>9560056</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>9560056.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>19.69</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>19.68</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>7704246.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>12926009.4</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>12926009.4</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>12343795.4</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>9938983.82</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>9938983.82</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>597764.8872133158</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>7704246</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>7704246.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>19.71</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>19.6</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>14533855.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>15923906.4</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>15923906.4</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>12138484.6</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>9970530.48</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>9970530.48</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>1146105.40044219</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>14533855</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>14533855.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>19.59</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>19.61</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>19.61</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>11998002.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>16512463.4</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>16512463.4</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>11779440.5</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>9887302.3</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>9887302.300000001</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>1156772.833610507</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>11998002</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>11998002.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>19.63</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>19.73</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>19.64</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>15496343.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>14972101.6</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>14972101.6</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>11232403.9</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>9953079.7</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>9953079.699999999</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>1402397.244079156</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>15496343</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>15496343.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>19.56</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>19.65</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>14897601.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>12457760.2</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>12457760.2</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>10341626.7</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>9752672.9</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>9752672.9</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>1328381.393174399</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>14897601</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>14897601.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>19.37</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>19.71</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>19.65</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>22693731.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>11761581.4</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>11761581.4</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>9475789.4</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>9540707.58</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>9540707.58</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>1239353.199268518</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>22693731</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>22693731.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>19.3</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>19.68</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>19.66</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>17476640.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>8353062.8</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>8353062.8</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>7990361.3</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>9181936.96</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>9181936.960000001</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>232607.8080005273</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>17476640</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>17476640.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>19.44</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>19.67</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>4296193.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>7046417.6</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>7046417.6</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>7117278.0</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>9005352.36</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>9005352.359999999</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-654933.2798109073</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>4296193</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>4296193.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
